--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/LOUISIANA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/LOUISIANA_2013.xlsx
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C136">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C389">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C709">
